--- a/uploads/phno.xlsx
+++ b/uploads/phno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saad Ali\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8A8713-4110-4518-8EB5-1BA0BECE123F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755214FD-A8B6-4959-92F4-36BAB371DA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FA831134-C2BD-477F-95A1-959AFA210AD8}"/>
   </bookViews>
@@ -33,10 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,13 +407,7 @@
   <cols>
     <col min="1" max="1" width="26.54296875" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1">
-        <v>3021960214</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>